--- a/artfynd/A 10673-2024 artfynd.xlsx
+++ b/artfynd/A 10673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116620102</v>
+        <v>116616278</v>
       </c>
       <c r="B2" t="n">
-        <v>100032</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fröåsa (Fröåsa), Sm</t>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532079</v>
+        <v>532164</v>
       </c>
       <c r="R2" t="n">
-        <v>6357378</v>
+        <v>6357430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,16 +780,11 @@
         <v>116617537</v>
       </c>
       <c r="B3" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,7 +808,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spinkakärr (Spinkakärr), Sm</t>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -884,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116616278</v>
+        <v>116619416</v>
       </c>
       <c r="B4" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spinkakärr (Spinkakärr), Sm</t>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532164</v>
+        <v>532139</v>
       </c>
       <c r="R4" t="n">
-        <v>6357430</v>
+        <v>6357507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116617386</v>
+        <v>116616829</v>
       </c>
       <c r="B5" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,19 +1011,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spinkakärr (Spinkakärr), Sm</t>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532190</v>
+        <v>532213</v>
       </c>
       <c r="R5" t="n">
-        <v>6357480</v>
+        <v>6357527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1079,503 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116617095</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532196</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6357522</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116617386</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6357480</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116618728</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spinkakärr, Spinkakärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532184</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6357514</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116615657</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fröåsa, Fröåsa, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>532083</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6357315</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116620102</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fröåsa, Fröåsa, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532079</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6357378</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10673-2024 artfynd.xlsx
+++ b/artfynd/A 10673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116619416</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116620102</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116616278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116617537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116616829</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116617095</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116617386</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1576,8 +1621,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116618728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>